--- a/static/data/exports/Retro_TR_AE_2008.xlsx
+++ b/static/data/exports/Retro_TR_AE_2008.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_AE_2008.xlsx
+++ b/static/data/exports/Retro_TR_AE_2008.xlsx
@@ -540,11 +540,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E2" t="n">
         <v>14439</v>
@@ -850,11 +850,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E7" t="n">
         <v>12993</v>
@@ -1036,11 +1036,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E10" t="n">
         <v>17324</v>
@@ -1346,11 +1346,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E15" t="n">
         <v>24853</v>
@@ -1718,11 +1718,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E21" t="n">
         <v>18833</v>
@@ -2028,11 +2028,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E26" t="n">
         <v>19194</v>
@@ -2338,11 +2338,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E31" t="n">
         <v>14198</v>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E35" t="n">
         <v>10965</v>
@@ -3206,11 +3206,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E45" t="n">
         <v>17745</v>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E48" t="n">
         <v>16605</v>
@@ -3702,11 +3702,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E53" t="n">
         <v>12470</v>
@@ -4074,11 +4074,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E59" t="n">
         <v>32105</v>
@@ -4446,11 +4446,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E65" t="n">
         <v>29349</v>
@@ -4818,11 +4818,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E71" t="n">
         <v>17042</v>
@@ -5190,11 +5190,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E77" t="n">
         <v>15457</v>
@@ -5438,11 +5438,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E81" t="n">
         <v>13990</v>
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E86" t="n">
         <v>14216</v>
@@ -5996,11 +5996,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E90" t="n">
         <v>13791</v>
@@ -6306,11 +6306,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E95" t="n">
         <v>14748</v>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E101" t="n">
         <v>14008</v>
@@ -6864,11 +6864,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E104" t="n">
         <v>17992</v>
@@ -7112,11 +7112,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E108" t="n">
         <v>11611</v>
@@ -7546,11 +7546,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E115" t="n">
         <v>15385</v>
@@ -7918,11 +7918,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E121" t="n">
         <v>13765</v>
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E126" t="n">
         <v>14972</v>
@@ -8662,11 +8662,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E133" t="n">
         <v>12653</v>
@@ -8972,11 +8972,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E138" t="n">
         <v>13325</v>
@@ -9158,11 +9158,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E141" t="n">
         <v>14816</v>
@@ -9406,11 +9406,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E145" t="n">
         <v>14979</v>
@@ -10212,11 +10212,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E158" t="n">
         <v>15601</v>
@@ -10460,11 +10460,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E162" t="n">
         <v>16659</v>
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E166" t="n">
         <v>22111</v>
@@ -11080,11 +11080,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E172" t="n">
         <v>15971</v>
@@ -11638,11 +11638,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E181" t="n">
         <v>19610</v>
@@ -11886,11 +11886,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E185" t="n">
         <v>13864</v>
@@ -12196,11 +12196,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E190" t="n">
         <v>21100</v>
@@ -12444,11 +12444,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E194" t="n">
         <v>19181</v>
@@ -12816,11 +12816,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E200" t="n">
         <v>14284</v>
@@ -13188,11 +13188,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E206" t="n">
         <v>18262</v>
@@ -13498,11 +13498,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E211" t="n">
         <v>19120</v>
@@ -13994,11 +13994,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E219" t="n">
         <v>11704</v>
@@ -14304,11 +14304,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E224" t="n">
         <v>14359</v>
@@ -14738,11 +14738,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E231" t="n">
         <v>14354</v>
@@ -15172,11 +15172,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E238" t="n">
         <v>14829</v>
@@ -15420,11 +15420,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E242" t="n">
         <v>12329</v>
@@ -15730,11 +15730,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E247" t="n">
         <v>17354</v>
@@ -16040,11 +16040,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E252" t="n">
         <v>14457</v>
@@ -16536,11 +16536,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E260" t="n">
         <v>17565</v>
@@ -16970,11 +16970,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E267" t="n">
         <v>16088</v>
@@ -17280,11 +17280,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E272" t="n">
         <v>14337</v>
@@ -17714,11 +17714,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E279" t="n">
         <v>12656</v>
@@ -18210,11 +18210,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E287" t="n">
         <v>13577</v>
@@ -18582,11 +18582,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E293" t="n">
         <v>14710</v>
@@ -18830,11 +18830,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E297" t="n">
         <v>17210</v>
@@ -19264,11 +19264,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E304" t="n">
         <v>13942</v>
@@ -19636,11 +19636,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E310" t="n">
         <v>13952</v>
